--- a/uploads/valid_yassine el  jabri.xlsx
+++ b/uploads/valid_yassine el  jabri.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>TEL CLIENT</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>0611250473</t>
-  </si>
-  <si>
-    <t>0611111111</t>
   </si>
 </sst>
 </file>
@@ -389,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -425,17 +422,6 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>999</v>
-      </c>
-      <c r="C4">
-        <v>999</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
